--- a/users.xlsx
+++ b/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D456A5-1A25-4FB6-83F1-9B8541E9DFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA3789F-F7CA-415C-9BF6-5E34A300CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
+    <workbookView xWindow="6250" yWindow="2790" windowWidth="8775" windowHeight="7290" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
     <t>New Zealand</t>
   </si>
   <si>
-    <t>Sai Chunduru</t>
+    <t>Sai-X1</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA3789F-F7CA-415C-9BF6-5E34A300CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D721EC6C-6C74-426A-B930-1A57A243803F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6250" yWindow="2790" windowWidth="8775" windowHeight="7290" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
+    <workbookView xWindow="1415" yWindow="1415" windowWidth="12960" windowHeight="7290" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,16 +59,16 @@
     <t>Portugal</t>
   </si>
   <si>
-    <t>Japan</t>
-  </si>
-  <si>
     <t>Norway</t>
   </si>
   <si>
-    <t>New Zealand</t>
-  </si>
-  <si>
-    <t>Sai-X1</t>
+    <t>Ice X1</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Czechia</t>
   </si>
 </sst>
 </file>
@@ -475,24 +475,21 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D721EC6C-6C74-426A-B930-1A57A243803F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0A83A9-0AEB-45F5-802F-AA83FCEE14F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1415" yWindow="1415" windowWidth="12960" windowHeight="7290" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Pot A</t>
   </si>
@@ -69,6 +69,33 @@
   </si>
   <si>
     <t>Czechia</t>
+  </si>
+  <si>
+    <t>erling haaland</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Lionel Ronaldo</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
   </si>
 </sst>
 </file>
@@ -447,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -491,6 +518,40 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0A83A9-0AEB-45F5-802F-AA83FCEE14F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9E4764-16D8-4B41-BB1F-8273E325FDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
   <si>
     <t>Pot A</t>
   </si>
@@ -96,6 +96,69 @@
   </si>
   <si>
     <t>New Zealand</t>
+  </si>
+  <si>
+    <t>Vai Brasil!!!!</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sereia </t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Auzzie AzzMah</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Côte d’Ivoire</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>HIghfield XI</t>
+  </si>
+  <si>
+    <t>QuadrennialViewer</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>Lil Nolzy lad</t>
+  </si>
+  <si>
+    <t>Not The Real Ronaldo</t>
+  </si>
+  <si>
+    <t>Cabo Verde</t>
+  </si>
+  <si>
+    <t>Ledger Legends</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>Kvaradona</t>
+  </si>
+  <si>
+    <t>Spain</t>
   </si>
 </sst>
 </file>
@@ -474,11 +537,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
-    <col min="4" max="4" width="11.2265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.76953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.75">
@@ -552,6 +615,159 @@
         <v>18</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9E4764-16D8-4B41-BB1F-8273E325FDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0532C8DB-D847-471A-8A20-724D72C77760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
   <si>
     <t>Pot A</t>
   </si>
@@ -159,6 +159,42 @@
   </si>
   <si>
     <t>Spain</t>
+  </si>
+  <si>
+    <t>The Craw</t>
+  </si>
+  <si>
+    <t>Pique Blinders</t>
+  </si>
+  <si>
+    <t>Angus</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Curaçao</t>
+  </si>
+  <si>
+    <t>It's Coming Home</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Gwinyeo</t>
+  </si>
+  <si>
+    <t>GemmaMorgan</t>
+  </si>
+  <si>
+    <t>DRedmond</t>
+  </si>
+  <si>
+    <t>Scorerg</t>
+  </si>
+  <si>
+    <t>Egypt</t>
   </si>
 </sst>
 </file>
@@ -537,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -768,6 +804,142 @@
         <v>28</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0532C8DB-D847-471A-8A20-724D72C77760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D5A833-726B-45BD-89B6-C95FD56D7A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
   <si>
     <t>Pot A</t>
   </si>
@@ -195,6 +195,42 @@
   </si>
   <si>
     <t>Egypt</t>
+  </si>
+  <si>
+    <t>EPipes</t>
+  </si>
+  <si>
+    <t>Tapu Oner</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Kaki Bangku</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Wildcats</t>
+  </si>
+  <si>
+    <t>SoccerBrews</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Aaron O'Haggis</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>IR Iran</t>
+  </si>
+  <si>
+    <t>Iraq</t>
   </si>
 </sst>
 </file>
@@ -573,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -940,6 +976,108 @@
         <v>28</v>
       </c>
     </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D5A833-726B-45BD-89B6-C95FD56D7A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0099621B-7ED4-4A04-8C34-266B0E4FD58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="68">
   <si>
     <t>Pot A</t>
   </si>
@@ -231,6 +231,18 @@
   </si>
   <si>
     <t>Iraq</t>
+  </si>
+  <si>
+    <t>CR7 The Goat</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Sam Kelly</t>
+  </si>
+  <si>
+    <t>Sinnamon</t>
   </si>
 </sst>
 </file>
@@ -609,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -1078,6 +1090,57 @@
         <v>63</v>
       </c>
     </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A30" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0099621B-7ED4-4A04-8C34-266B0E4FD58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207ED6FE-D4CF-4EE9-8034-22332FF86E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
+    <workbookView xWindow="8565" yWindow="0" windowWidth="8790" windowHeight="10155" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="73">
   <si>
     <t>Pot A</t>
   </si>
@@ -243,6 +243,21 @@
   </si>
   <si>
     <t>Sinnamon</t>
+  </si>
+  <si>
+    <t>Gavi and Stacey</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>ATFC</t>
+  </si>
+  <si>
+    <t>Sophie Grujevski</t>
+  </si>
+  <si>
+    <t>EdrikLee</t>
   </si>
 </sst>
 </file>
@@ -621,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -1141,6 +1156,74 @@
         <v>28</v>
       </c>
     </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A33" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207ED6FE-D4CF-4EE9-8034-22332FF86E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AACB4BC-4D7F-4C94-889D-3E55C3BA7DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8565" yWindow="0" windowWidth="8790" windowHeight="10155" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="74">
   <si>
     <t>Pot A</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>EdrikLee</t>
+  </si>
+  <si>
+    <t>NathanCleary4DallyM</t>
   </si>
 </sst>
 </file>
@@ -636,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -1224,6 +1227,23 @@
         <v>28</v>
       </c>
     </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A35" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AACB4BC-4D7F-4C94-889D-3E55C3BA7DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA130040-46B8-4022-B8DC-3DFF2C394D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
   <si>
     <t>Pot A</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>NathanCleary4DallyM</t>
+  </si>
+  <si>
+    <t>winningteam</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
   </si>
 </sst>
 </file>
@@ -639,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -1244,6 +1250,23 @@
         <v>28</v>
       </c>
     </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A36" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA130040-46B8-4022-B8DC-3DFF2C394D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C4475E-8363-4F6F-A9EA-045A311E51BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="78">
   <si>
     <t>Pot A</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>AuditWizard</t>
+  </si>
+  <si>
+    <t>It's Coming Home1</t>
   </si>
 </sst>
 </file>
@@ -645,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -1267,6 +1273,40 @@
         <v>14</v>
       </c>
     </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A37" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/users.xlsx
+++ b/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saichunduru\fifa wc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C4475E-8363-4F6F-A9EA-045A311E51BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1830E0B-213B-47FB-889C-DBE43DCAF4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="17460" windowHeight="10260" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
+    <workbookView xWindow="2135" yWindow="2135" windowWidth="12960" windowHeight="7290" xr2:uid="{E67833B8-4FEA-401B-A1B4-AB5D5161C38E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="83">
   <si>
     <t>Pot A</t>
   </si>
@@ -273,6 +273,21 @@
   </si>
   <si>
     <t>It's Coming Home1</t>
+  </si>
+  <si>
+    <t>Lavina</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Lukas</t>
+  </si>
+  <si>
+    <t>Canada</t>
   </si>
 </sst>
 </file>
@@ -651,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1271A6DF-7B4F-4F21-A272-DFA4D7BFB8B4}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="21.04296875" customWidth="1"/>
@@ -1307,6 +1322,40 @@
         <v>14</v>
       </c>
     </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
